--- a/Result/DivideRBM_RQAE_eps0=2^-8_R=12_maxdeg=10_integEpsabs=1e-4.xlsx
+++ b/Result/DivideRBM_RQAE_eps0=2^-8_R=12_maxdeg=10_integEpsabs=1e-4.xlsx
@@ -1,26 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koich\Desktop\Code\DivQCOSDE\Result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{044D48EF-BB1C-4675-9C27-1A57E06E7E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F730FC98-F98C-41C9-A0C6-57249AD113C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DDFBC754-980A-4BFD-AE2C-311ED991EAD0}"/>
+    <workbookView xWindow="0" yWindow="705" windowWidth="18390" windowHeight="9015" xr2:uid="{DDFBC754-980A-4BFD-AE2C-311ED991EAD0}"/>
   </bookViews>
   <sheets>
     <sheet name="DivideRBM_RQAE_eps0=2^-8_R=12_m" sheetId="1" r:id="rId1"/>
+    <sheet name="追加データ" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="13">
   <si>
     <t>N</t>
   </si>
@@ -77,13 +91,30 @@
     </rPh>
     <phoneticPr fontId="18"/>
   </si>
+  <si>
+    <t>RMSE=0.001を達成するのに必要な古典モンテサンプル数</t>
+    <rPh sb="11" eb="13">
+      <t>タッセイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コテン</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>スウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="179" formatCode="0.00000"/>
+  <numFmts count="2">
+    <numFmt numFmtId="176" formatCode="0.00000"/>
+    <numFmt numFmtId="177" formatCode="0.000000"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -674,20 +705,23 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -881,11 +915,122 @@
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
+          <c:idx val="2"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'DivideRBM_RQAE_eps0=2^-8_R=12_m'!$P$1</c:f>
+              <c:f>'DivideRBM_RQAE_eps0=2^-8_R=12_m'!$R$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>RMSE=0.001を達成するのに必要な古典モンテサンプル数</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'DivideRBM_RQAE_eps0=2^-8_R=12_m'!$J$2:$J$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>90</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'DivideRBM_RQAE_eps0=2^-8_R=12_m'!$R$2:$R$9</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0_);[Red]\(#,##0\)</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>3816749.7256402196</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5248030.8727553021</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7633499.4512804393</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10496061.745510604</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15266998.902560879</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>21469217.206726234</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30533997.805121757</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>42938434.413452469</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-63E6-4341-99FE-6CA6D6FC52C8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DivideRBM_RQAE_eps0=2^-8_R=12_m'!$Q$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -953,7 +1098,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'DivideRBM_RQAE_eps0=2^-8_R=12_m'!$P$2:$P$9</c:f>
+              <c:f>'DivideRBM_RQAE_eps0=2^-8_R=12_m'!$Q$2:$Q$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0_);[Red]\(#,##0\)</c:formatCode>
                 <c:ptCount val="8"/>
@@ -987,7 +1132,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3508-452A-866C-3D6397DB0CDC}"/>
+              <c16:uniqueId val="{00000000-0A44-408E-BE21-EA58B9980AB0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1071,7 +1216,7 @@
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
-          <c:min val="100000"/>
+          <c:min val="1000000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1779,10 +1924,10 @@
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>3486150</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>233362</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>3057525</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2127,15 +2272,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{449532EA-BAB9-471F-AFF2-8FC10C78FD9E}">
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:R79"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="13" max="13" width="14.875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="51.75" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="51.75" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2175,11 +2320,14 @@
       <c r="N1" t="s">
         <v>6</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="R1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>8</v>
       </c>
@@ -2209,28 +2357,31 @@
         <v>8</v>
       </c>
       <c r="K2" s="2">
-        <f t="shared" ref="K2:K10" si="0">AVERAGEIF($A$2:$A$1048576,$J2,$E$2:$E$1048576)</f>
+        <f t="shared" ref="K2:K9" si="0">AVERAGEIF($A$2:$A$1048576,$J2,$E$2:$E$1048576)</f>
         <v>6.3097625785145492E-4</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="5">
         <f>SQRT(AVERAGEIF($A$2:$A$1048576,$J2,$F$2:$F$1048576))</f>
         <v>8.0183704647156522E-4</v>
       </c>
       <c r="M2" s="3">
-        <f t="shared" ref="M2:M10" si="1">AVERAGEIF($A$2:$A$1048576,$J2,$G$2:$G$1048576)</f>
+        <f t="shared" ref="M2:M9" si="1">AVERAGEIF($A$2:$A$1048576,$J2,$G$2:$G$1048576)</f>
         <v>1324159.1000000001</v>
       </c>
       <c r="N2" s="4">
-        <f t="shared" ref="N2:N10" si="2">AVERAGEIF($A$2:$A$1048576,$J2,$H$2:$H$1048576)</f>
+        <f t="shared" ref="N2:N9" si="2">AVERAGEIF($A$2:$A$1048576,$J2,$H$2:$H$1048576)</f>
         <v>724</v>
       </c>
-      <c r="P2" s="3">
-        <f t="shared" ref="P2" si="3">J2/L2/L2*SQRT($B$2*(1-$B$2))</f>
+      <c r="Q2" s="3">
+        <f t="shared" ref="Q2:Q9" si="3">$J2/$L2/$L2*SQRT($B$2*(1-$B$2))</f>
         <v>5936376.644195457</v>
       </c>
-      <c r="Q2" s="3"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="R2" s="3">
+        <f t="shared" ref="R2:R9" si="4">$J2/(0.001^2)*SQRT($B$2*(1-$B$2))</f>
+        <v>3816749.7256402196</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>11</v>
       </c>
@@ -2247,7 +2398,7 @@
         <v>2.4947581689593803E-4</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F66" si="4">E3*E3</f>
+        <f t="shared" ref="F3:F66" si="5">E3*E3</f>
         <v>6.2238183215895602E-8</v>
       </c>
       <c r="G3">
@@ -2263,8 +2414,8 @@
         <f t="shared" si="0"/>
         <v>6.1892908040802577E-4</v>
       </c>
-      <c r="L3" s="2">
-        <f t="shared" ref="L3:L8" si="5">SQRT(AVERAGEIF($A$2:$A$1048576,$J3,$F$2:$F$1048576))</f>
+      <c r="L3" s="5">
+        <f t="shared" ref="L3:L8" si="6">SQRT(AVERAGEIF($A$2:$A$1048576,$J3,$F$2:$F$1048576))</f>
         <v>8.0420424353400024E-4</v>
       </c>
       <c r="M3" s="3">
@@ -2275,13 +2426,16 @@
         <f t="shared" si="2"/>
         <v>848.9</v>
       </c>
-      <c r="P3" s="3">
-        <f>J3/L3/L3*SQRT($B$2*(1-$B$2))</f>
+      <c r="Q3" s="3">
+        <f t="shared" si="3"/>
         <v>8114535.4219214227</v>
       </c>
-      <c r="Q3" s="3"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="R3" s="3">
+        <f t="shared" si="4"/>
+        <v>5248030.8727553021</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>16</v>
       </c>
@@ -2298,7 +2452,7 @@
         <v>1.01080646133211E-3</v>
       </c>
       <c r="F4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.0217297022707425E-6</v>
       </c>
       <c r="G4">
@@ -2314,8 +2468,8 @@
         <f t="shared" si="0"/>
         <v>1.168866886688678E-3</v>
       </c>
-      <c r="L4" s="2">
-        <f t="shared" si="5"/>
+      <c r="L4" s="5">
+        <f t="shared" si="6"/>
         <v>1.411880554135925E-3</v>
       </c>
       <c r="M4" s="3">
@@ -2326,13 +2480,16 @@
         <f t="shared" si="2"/>
         <v>1022.9</v>
       </c>
-      <c r="P4" s="3">
-        <f>J4/L4/L4*SQRT($B$2*(1-$B$2))</f>
+      <c r="Q4" s="3">
+        <f t="shared" si="3"/>
         <v>3829373.8325180993</v>
       </c>
-      <c r="Q4" s="3"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="R4" s="3">
+        <f t="shared" si="4"/>
+        <v>7633499.4512804393</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>22</v>
       </c>
@@ -2349,7 +2506,7 @@
         <v>5.4012988230234195E-4</v>
       </c>
       <c r="F5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.9174028975594179E-7</v>
       </c>
       <c r="G5">
@@ -2365,8 +2522,8 @@
         <f t="shared" si="0"/>
         <v>6.9892971910899657E-4</v>
       </c>
-      <c r="L5" s="2">
-        <f t="shared" si="5"/>
+      <c r="L5" s="5">
+        <f t="shared" si="6"/>
         <v>8.767930322703078E-4</v>
       </c>
       <c r="M5" s="3">
@@ -2377,13 +2534,16 @@
         <f t="shared" si="2"/>
         <v>1200</v>
       </c>
-      <c r="P5" s="3">
-        <f>J5/L5/L5*SQRT($B$2*(1-$B$2))</f>
+      <c r="Q5" s="3">
+        <f t="shared" si="3"/>
         <v>13653129.109271333</v>
       </c>
-      <c r="Q5" s="3"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="R5" s="3">
+        <f t="shared" si="4"/>
+        <v>10496061.745510604</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>32</v>
       </c>
@@ -2400,7 +2560,7 @@
         <v>6.0224546886111698E-4</v>
       </c>
       <c r="F6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.6269960476374661E-7</v>
       </c>
       <c r="G6">
@@ -2416,8 +2576,8 @@
         <f t="shared" si="0"/>
         <v>7.3249512451248788E-4</v>
       </c>
-      <c r="L6" s="2">
-        <f t="shared" si="5"/>
+      <c r="L6" s="5">
+        <f t="shared" si="6"/>
         <v>8.7045867004054915E-4</v>
       </c>
       <c r="M6" s="3">
@@ -2428,13 +2588,16 @@
         <f t="shared" si="2"/>
         <v>1448</v>
       </c>
-      <c r="P6" s="3">
-        <f t="shared" ref="P6:P10" si="6">J6/L6/L6*SQRT($B$2*(1-$B$2))</f>
+      <c r="Q6" s="3">
+        <f t="shared" si="3"/>
         <v>20149179.40048863</v>
       </c>
-      <c r="Q6" s="3"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="R6" s="3">
+        <f t="shared" si="4"/>
+        <v>15266998.902560879</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>45</v>
       </c>
@@ -2451,7 +2614,7 @@
         <v>1.1166764233282399E-3</v>
       </c>
       <c r="F7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.2469662344171504E-6</v>
       </c>
       <c r="G7">
@@ -2467,8 +2630,8 @@
         <f t="shared" si="0"/>
         <v>4.9158957486898852E-4</v>
       </c>
-      <c r="L7" s="2">
-        <f t="shared" si="5"/>
+      <c r="L7" s="5">
+        <f t="shared" si="6"/>
         <v>6.414906712376735E-4</v>
       </c>
       <c r="M7" s="3">
@@ -2479,13 +2642,16 @@
         <f t="shared" si="2"/>
         <v>1717</v>
       </c>
-      <c r="P7" s="3">
-        <f t="shared" si="6"/>
+      <c r="Q7" s="3">
+        <f t="shared" si="3"/>
         <v>52171763.824922092</v>
       </c>
-      <c r="Q7" s="3"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="R7" s="3">
+        <f t="shared" si="4"/>
+        <v>21469217.206726234</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>64</v>
       </c>
@@ -2502,7 +2668,7 @@
         <v>5.1896040172583202E-4</v>
       </c>
       <c r="F8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.6931989855943697E-7</v>
       </c>
       <c r="G8">
@@ -2518,8 +2684,8 @@
         <f t="shared" si="0"/>
         <v>5.7598037531181247E-4</v>
       </c>
-      <c r="L8" s="2">
-        <f t="shared" si="5"/>
+      <c r="L8" s="5">
+        <f t="shared" si="6"/>
         <v>6.3861609822621367E-4</v>
       </c>
       <c r="M8" s="3">
@@ -2530,13 +2696,16 @@
         <f t="shared" si="2"/>
         <v>2047</v>
       </c>
-      <c r="P8" s="3">
-        <f t="shared" si="6"/>
+      <c r="Q8" s="3">
+        <f t="shared" si="3"/>
         <v>74869329.879273564</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="R8" s="3">
+        <f t="shared" si="4"/>
+        <v>30533997.805121757</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2553,7 +2722,7 @@
         <v>2.6822769208334398E-4</v>
       </c>
       <c r="F9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7.1946094800357195E-8</v>
       </c>
       <c r="G9">
@@ -2569,7 +2738,7 @@
         <f t="shared" si="0"/>
         <v>6.1695622687277165E-4</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="5">
         <f>SQRT(AVERAGEIF($A$2:$A$1048576,$J9,$F$2:$F$1048576))</f>
         <v>8.3893859519543982E-4</v>
       </c>
@@ -2581,13 +2750,16 @@
         <f t="shared" si="2"/>
         <v>2428</v>
       </c>
-      <c r="P9" s="3">
-        <f t="shared" si="6"/>
+      <c r="Q9" s="3">
+        <f t="shared" si="3"/>
         <v>61007869.16034776</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="R9" s="3">
+        <f t="shared" si="4"/>
+        <v>42938434.413452469</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>11</v>
       </c>
@@ -2604,7 +2776,7 @@
         <v>9.5384312862711797E-4</v>
       </c>
       <c r="F10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.0981671402916877E-7</v>
       </c>
       <c r="G10">
@@ -2612,18 +2784,15 @@
       </c>
       <c r="H10">
         <v>849</v>
-      </c>
-      <c r="J10">
-        <v>128</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="3"/>
       <c r="N10" s="4"/>
-      <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>16</v>
       </c>
@@ -2640,7 +2809,7 @@
         <v>3.5410016570236398E-4</v>
       </c>
       <c r="F11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.2538692735044163E-7</v>
       </c>
       <c r="G11">
@@ -2650,7 +2819,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>22</v>
       </c>
@@ -2667,7 +2836,7 @@
         <v>2.7753000868657702E-4</v>
       </c>
       <c r="F12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7.7022905721571513E-8</v>
       </c>
       <c r="G12">
@@ -2677,7 +2846,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>32</v>
       </c>
@@ -2694,7 +2863,7 @@
         <v>6.6077145783172099E-4</v>
       </c>
       <c r="F13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.3661891948505781E-7</v>
       </c>
       <c r="G13">
@@ -2704,7 +2873,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>45</v>
       </c>
@@ -2721,7 +2890,7 @@
         <v>7.1741774746036902E-4</v>
       </c>
       <c r="F14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.1468822437110978E-7</v>
       </c>
       <c r="G14">
@@ -2731,7 +2900,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>64</v>
       </c>
@@ -2748,7 +2917,7 @@
         <v>5.0848609292364301E-4</v>
       </c>
       <c r="F15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.5855810669675169E-7</v>
       </c>
       <c r="G15">
@@ -2758,7 +2927,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>90</v>
       </c>
@@ -2775,7 +2944,7 @@
         <v>4.3595853899791497E-5</v>
       </c>
       <c r="F16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.9005984772519655E-9</v>
       </c>
       <c r="G16">
@@ -2802,7 +2971,7 @@
         <v>7.87420236337821E-4</v>
       </c>
       <c r="F17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6.200306285943099E-7</v>
       </c>
       <c r="G17">
@@ -2829,7 +2998,7 @@
         <v>1.23427285871891E-5</v>
       </c>
       <c r="F18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.5234294897701503E-10</v>
       </c>
       <c r="G18">
@@ -2856,7 +3025,7 @@
         <v>1.0093174260568101E-3</v>
       </c>
       <c r="F19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.0187216665419443E-6</v>
       </c>
       <c r="G19">
@@ -2883,7 +3052,7 @@
         <v>9.2525103078877602E-4</v>
       </c>
       <c r="F20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8.5608946997569256E-7</v>
       </c>
       <c r="G20">
@@ -2910,7 +3079,7 @@
         <v>1.03580896158195E-3</v>
       </c>
       <c r="F21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.0729002048934775E-6</v>
       </c>
       <c r="G21">
@@ -2937,7 +3106,7 @@
         <v>3.3073394270832698E-4</v>
       </c>
       <c r="F22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.0938494085939491E-7</v>
       </c>
       <c r="G22">
@@ -2964,7 +3133,7 @@
         <v>1.5017352303814399E-4</v>
       </c>
       <c r="F23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.2552087021687965E-8</v>
       </c>
       <c r="G23">
@@ -2991,7 +3160,7 @@
         <v>1.2355119205061901E-3</v>
       </c>
       <c r="F24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.526489705712894E-6</v>
       </c>
       <c r="G24">
@@ -3018,7 +3187,7 @@
         <v>1.3767227291316901E-4</v>
       </c>
       <c r="F25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.8953654729078091E-8</v>
       </c>
       <c r="G25">
@@ -3045,7 +3214,7 @@
         <v>4.43035610417918E-5</v>
       </c>
       <c r="F26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.9628055209837722E-9</v>
       </c>
       <c r="G26">
@@ -3072,7 +3241,7 @@
         <v>1.2827086515508901E-3</v>
       </c>
       <c r="F27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.6453414847635029E-6</v>
       </c>
       <c r="G27">
@@ -3099,7 +3268,7 @@
         <v>9.19000405726233E-4</v>
       </c>
       <c r="F28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8.4456174572498086E-7</v>
       </c>
       <c r="G28">
@@ -3126,7 +3295,7 @@
         <v>1.86487173148719E-3</v>
       </c>
       <c r="F29">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.47774657490003E-6</v>
       </c>
       <c r="G29">
@@ -3153,7 +3322,7 @@
         <v>7.9718028661579493E-6</v>
       </c>
       <c r="F30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6.3549640936884099E-11</v>
       </c>
       <c r="G30">
@@ -3180,7 +3349,7 @@
         <v>6.8350359467350599E-4</v>
       </c>
       <c r="F31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.6717716393160438E-7</v>
       </c>
       <c r="G31">
@@ -3207,7 +3376,7 @@
         <v>2.2251999631395201E-4</v>
       </c>
       <c r="F32">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.9515148759561216E-8</v>
       </c>
       <c r="G32">
@@ -3234,7 +3403,7 @@
         <v>1.03815294598041E-3</v>
       </c>
       <c r="F33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.0777615392478039E-6</v>
       </c>
       <c r="G33">
@@ -3261,7 +3430,7 @@
         <v>6.3069032471818598E-4</v>
       </c>
       <c r="F34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.9777028569313089E-7</v>
       </c>
       <c r="G34">
@@ -3288,7 +3457,7 @@
         <v>3.4596984129842102E-4</v>
       </c>
       <c r="F35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.1969513108805462E-7</v>
       </c>
       <c r="G35">
@@ -3315,7 +3484,7 @@
         <v>1.4726450088150499E-3</v>
       </c>
       <c r="F36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.1686833219878785E-6</v>
       </c>
       <c r="G36">
@@ -3342,7 +3511,7 @@
         <v>1.40016257311637E-4</v>
       </c>
       <c r="F37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.9604552311558543E-8</v>
       </c>
       <c r="G37">
@@ -3369,7 +3538,7 @@
         <v>5.7951333201911005E-4</v>
       </c>
       <c r="F38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.3583570198789129E-7</v>
       </c>
       <c r="G38">
@@ -3396,7 +3565,7 @@
         <v>9.9596122680844991E-4</v>
       </c>
       <c r="F39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.9193876530579255E-7</v>
       </c>
       <c r="G39">
@@ -3423,7 +3592,7 @@
         <v>7.6280840015430197E-4</v>
       </c>
       <c r="F40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.8187665534596564E-7</v>
       </c>
       <c r="G40">
@@ -3450,7 +3619,7 @@
         <v>4.6434105341952499E-4</v>
       </c>
       <c r="F41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.1561261389075415E-7</v>
       </c>
       <c r="G41">
@@ -3477,7 +3646,7 @@
         <v>1.4613091995019299E-5</v>
       </c>
       <c r="F42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.1354245765489712E-10</v>
       </c>
       <c r="G42">
@@ -3504,7 +3673,7 @@
         <v>5.7489898421281195E-4</v>
       </c>
       <c r="F43">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.3050884204892303E-7</v>
       </c>
       <c r="G43">
@@ -3531,7 +3700,7 @@
         <v>1.7651787735629601E-3</v>
       </c>
       <c r="F44">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.1158561026372359E-6</v>
       </c>
       <c r="G44">
@@ -3558,7 +3727,7 @@
         <v>8.9368086240049205E-4</v>
       </c>
       <c r="F45">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7.9866548382088717E-7</v>
       </c>
       <c r="G45">
@@ -3585,7 +3754,7 @@
         <v>1.96662546940507E-4</v>
       </c>
       <c r="F46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.867615736912712E-8</v>
       </c>
       <c r="G46">
@@ -3612,7 +3781,7 @@
         <v>1.22827038389505E-4</v>
       </c>
       <c r="F47">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.5086481359536936E-8</v>
       </c>
       <c r="G47">
@@ -3639,7 +3808,7 @@
         <v>1.7651787735631899E-3</v>
       </c>
       <c r="F48">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.1158561026380474E-6</v>
       </c>
       <c r="G48">
@@ -3666,7 +3835,7 @@
         <v>3.9082258794464998E-4</v>
       </c>
       <c r="F49">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.5274229524775366E-7</v>
       </c>
       <c r="G49">
@@ -3693,7 +3862,7 @@
         <v>6.0341746106018501E-4</v>
       </c>
       <c r="F50">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.6411263231231991E-7</v>
       </c>
       <c r="G50">
@@ -3720,7 +3889,7 @@
         <v>1.4831929386079901E-3</v>
       </c>
       <c r="F51">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.1998612931366052E-6</v>
       </c>
       <c r="G51">
@@ -3747,7 +3916,7 @@
         <v>2.0611210552468E-4</v>
       </c>
       <c r="F52">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.2482200043816823E-8</v>
       </c>
       <c r="G52">
@@ -3774,7 +3943,7 @@
         <v>3.4401652096638298E-4</v>
       </c>
       <c r="F53">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.1834736669781382E-7</v>
       </c>
       <c r="G53">
@@ -3801,7 +3970,7 @@
         <v>1.16082146283214E-3</v>
       </c>
       <c r="F54">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.3475064685717495E-6</v>
       </c>
       <c r="G54">
@@ -3828,7 +3997,7 @@
         <v>7.0686981766754299E-4</v>
       </c>
       <c r="F55">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.9966493912934546E-7</v>
       </c>
       <c r="G55">
@@ -3855,7 +4024,7 @@
         <v>3.12299110596936E-4</v>
       </c>
       <c r="F56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.7530734479637266E-8</v>
       </c>
       <c r="G56">
@@ -3882,7 +4051,7 @@
         <v>3.9558417773177801E-4</v>
       </c>
       <c r="F57">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.5648684167172693E-7</v>
       </c>
       <c r="G57">
@@ -3909,7 +4078,7 @@
         <v>1.0541701727031501E-3</v>
       </c>
       <c r="F58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.1112747530169892E-6</v>
       </c>
       <c r="G58">
@@ -3936,7 +4105,7 @@
         <v>3.00788116880257E-3</v>
       </c>
       <c r="F59">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.0473491256371153E-6</v>
       </c>
       <c r="G59">
@@ -3963,7 +4132,7 @@
         <v>4.1269977566338301E-4</v>
       </c>
       <c r="F60">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.7032110483260667E-7</v>
       </c>
       <c r="G60">
@@ -3990,7 +4159,7 @@
         <v>9.5611349203506002E-4</v>
       </c>
       <c r="F61">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.1415300965147673E-7</v>
       </c>
       <c r="G61">
@@ -4017,7 +4186,7 @@
         <v>1.8519732659094601E-5</v>
       </c>
       <c r="F62">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.4298049776433516E-10</v>
       </c>
       <c r="G62">
@@ -4044,7 +4213,7 @@
         <v>8.2719435012079603E-4</v>
       </c>
       <c r="F63">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6.8425049287176603E-7</v>
       </c>
       <c r="G63">
@@ -4071,7 +4240,7 @@
         <v>9.5480553741311702E-5</v>
       </c>
       <c r="F64">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.116536142747512E-9</v>
       </c>
       <c r="G64">
@@ -4098,7 +4267,7 @@
         <v>1.92386200551475E-3</v>
       </c>
       <c r="F65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.7012450162632363E-6</v>
       </c>
       <c r="G65">
@@ -4125,7 +4294,7 @@
         <v>1.0209637270585099E-3</v>
       </c>
       <c r="F66">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.0423669319692034E-6</v>
       </c>
       <c r="G66">
@@ -4491,4 +4660,581 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DF08AE6-20C8-471A-AB3F-25B3245D227F}">
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A2">
+        <v>16</v>
+      </c>
+      <c r="B2">
+        <v>0.64960499999999999</v>
+      </c>
+      <c r="C2">
+        <v>9.77E-4</v>
+      </c>
+      <c r="D2">
+        <v>0.64820599999999995</v>
+      </c>
+      <c r="E2">
+        <v>1.3979999999999999E-3</v>
+      </c>
+      <c r="F2">
+        <f t="shared" ref="F2:F21" si="0">E2*E2</f>
+        <v>1.954404E-6</v>
+      </c>
+      <c r="G2">
+        <v>2930954</v>
+      </c>
+      <c r="H2">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>16</v>
+      </c>
+      <c r="B3">
+        <v>0.64960499999999999</v>
+      </c>
+      <c r="C3">
+        <v>9.77E-4</v>
+      </c>
+      <c r="D3">
+        <v>0.64903500000000003</v>
+      </c>
+      <c r="E3">
+        <v>5.6899999999999995E-4</v>
+      </c>
+      <c r="F3">
+        <f t="shared" si="0"/>
+        <v>3.2376099999999996E-7</v>
+      </c>
+      <c r="G3">
+        <v>2944081</v>
+      </c>
+      <c r="H3">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>16</v>
+      </c>
+      <c r="B4">
+        <v>0.64960499999999999</v>
+      </c>
+      <c r="C4">
+        <v>9.77E-4</v>
+      </c>
+      <c r="D4">
+        <v>0.65023399999999998</v>
+      </c>
+      <c r="E4">
+        <v>6.3000000000000003E-4</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>3.9690000000000001E-7</v>
+      </c>
+      <c r="G4">
+        <v>2932019</v>
+      </c>
+      <c r="H4">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>0.64960499999999999</v>
+      </c>
+      <c r="C5">
+        <v>9.77E-4</v>
+      </c>
+      <c r="D5">
+        <v>0.64991200000000005</v>
+      </c>
+      <c r="E5">
+        <v>3.0699999999999998E-4</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>9.4248999999999986E-8</v>
+      </c>
+      <c r="G5">
+        <v>2938667</v>
+      </c>
+      <c r="H5">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>16</v>
+      </c>
+      <c r="B6">
+        <v>0.64960499999999999</v>
+      </c>
+      <c r="C6">
+        <v>9.77E-4</v>
+      </c>
+      <c r="D6">
+        <v>0.64978400000000003</v>
+      </c>
+      <c r="E6">
+        <v>1.7899999999999999E-4</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>3.2040999999999996E-8</v>
+      </c>
+      <c r="G6">
+        <v>2942116</v>
+      </c>
+      <c r="H6">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>16</v>
+      </c>
+      <c r="B7">
+        <v>0.64960499999999999</v>
+      </c>
+      <c r="C7">
+        <v>9.77E-4</v>
+      </c>
+      <c r="D7">
+        <v>0.64989799999999998</v>
+      </c>
+      <c r="E7">
+        <v>2.9399999999999999E-4</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>8.6435999999999994E-8</v>
+      </c>
+      <c r="G7">
+        <v>2942763</v>
+      </c>
+      <c r="H7">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>0.64960499999999999</v>
+      </c>
+      <c r="C8">
+        <v>9.77E-4</v>
+      </c>
+      <c r="D8">
+        <v>0.65014700000000003</v>
+      </c>
+      <c r="E8">
+        <v>5.4199999999999995E-4</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>2.9376399999999996E-7</v>
+      </c>
+      <c r="G8">
+        <v>2937069</v>
+      </c>
+      <c r="H8">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>16</v>
+      </c>
+      <c r="B9">
+        <v>0.64960499999999999</v>
+      </c>
+      <c r="C9">
+        <v>9.77E-4</v>
+      </c>
+      <c r="D9">
+        <v>0.64969100000000002</v>
+      </c>
+      <c r="E9">
+        <v>8.6000000000000003E-5</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>7.3960000000000005E-9</v>
+      </c>
+      <c r="G9">
+        <v>2947463</v>
+      </c>
+      <c r="H9">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>16</v>
+      </c>
+      <c r="B10">
+        <v>0.64960499999999999</v>
+      </c>
+      <c r="C10">
+        <v>9.77E-4</v>
+      </c>
+      <c r="D10">
+        <v>0.65027000000000001</v>
+      </c>
+      <c r="E10">
+        <v>6.6500000000000001E-4</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>4.4222500000000003E-7</v>
+      </c>
+      <c r="G10">
+        <v>2938451</v>
+      </c>
+      <c r="H10">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>16</v>
+      </c>
+      <c r="B11">
+        <v>0.64960499999999999</v>
+      </c>
+      <c r="C11">
+        <v>9.77E-4</v>
+      </c>
+      <c r="D11">
+        <v>0.64920699999999998</v>
+      </c>
+      <c r="E11">
+        <v>3.9800000000000002E-4</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>1.5840400000000002E-7</v>
+      </c>
+      <c r="G11">
+        <v>2939201</v>
+      </c>
+      <c r="H11">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <v>16</v>
+      </c>
+      <c r="B12">
+        <v>0.64960499999999999</v>
+      </c>
+      <c r="C12">
+        <v>9.77E-4</v>
+      </c>
+      <c r="D12">
+        <v>0.649837</v>
+      </c>
+      <c r="E12">
+        <v>2.33E-4</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>5.4288999999999997E-8</v>
+      </c>
+      <c r="G12">
+        <v>2942364</v>
+      </c>
+      <c r="H12">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>16</v>
+      </c>
+      <c r="B13">
+        <v>0.64960499999999999</v>
+      </c>
+      <c r="C13">
+        <v>9.77E-4</v>
+      </c>
+      <c r="D13">
+        <v>0.64904700000000004</v>
+      </c>
+      <c r="E13">
+        <v>5.5800000000000001E-4</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>3.1136400000000001E-7</v>
+      </c>
+      <c r="G13">
+        <v>2936136</v>
+      </c>
+      <c r="H13">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>16</v>
+      </c>
+      <c r="B14">
+        <v>0.64960499999999999</v>
+      </c>
+      <c r="C14">
+        <v>9.77E-4</v>
+      </c>
+      <c r="D14">
+        <v>0.64942500000000003</v>
+      </c>
+      <c r="E14">
+        <v>1.7899999999999999E-4</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>3.2040999999999996E-8</v>
+      </c>
+      <c r="G14">
+        <v>2928456</v>
+      </c>
+      <c r="H14">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>16</v>
+      </c>
+      <c r="B15">
+        <v>0.64960499999999999</v>
+      </c>
+      <c r="C15">
+        <v>9.77E-4</v>
+      </c>
+      <c r="D15">
+        <v>0.65140900000000002</v>
+      </c>
+      <c r="E15">
+        <v>1.804E-3</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>3.2544160000000001E-6</v>
+      </c>
+      <c r="G15">
+        <v>2958138</v>
+      </c>
+      <c r="H15">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>0.64960499999999999</v>
+      </c>
+      <c r="C16">
+        <v>9.77E-4</v>
+      </c>
+      <c r="D16">
+        <v>0.64957399999999998</v>
+      </c>
+      <c r="E16">
+        <v>3.1000000000000001E-5</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>9.6100000000000009E-10</v>
+      </c>
+      <c r="G16">
+        <v>2942290</v>
+      </c>
+      <c r="H16">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>0.64960499999999999</v>
+      </c>
+      <c r="C17">
+        <v>9.77E-4</v>
+      </c>
+      <c r="D17">
+        <v>0.649227</v>
+      </c>
+      <c r="E17">
+        <v>3.7800000000000003E-4</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>1.4288400000000002E-7</v>
+      </c>
+      <c r="G17">
+        <v>2949898</v>
+      </c>
+      <c r="H17">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>0.64960499999999999</v>
+      </c>
+      <c r="C18">
+        <v>9.77E-4</v>
+      </c>
+      <c r="D18">
+        <v>0.64979200000000004</v>
+      </c>
+      <c r="E18">
+        <v>1.8699999999999999E-4</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>3.4968999999999994E-8</v>
+      </c>
+      <c r="G18">
+        <v>2923176</v>
+      </c>
+      <c r="H18">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19">
+        <v>0.64960499999999999</v>
+      </c>
+      <c r="C19">
+        <v>9.77E-4</v>
+      </c>
+      <c r="D19">
+        <v>0.64950699999999995</v>
+      </c>
+      <c r="E19">
+        <v>9.7E-5</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>9.4090000000000001E-9</v>
+      </c>
+      <c r="G19">
+        <v>2937022</v>
+      </c>
+      <c r="H19">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>16</v>
+      </c>
+      <c r="B20">
+        <v>0.64960499999999999</v>
+      </c>
+      <c r="C20">
+        <v>9.77E-4</v>
+      </c>
+      <c r="D20">
+        <v>0.64955499999999999</v>
+      </c>
+      <c r="E20">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>2.5000000000000001E-9</v>
+      </c>
+      <c r="G20">
+        <v>2941749</v>
+      </c>
+      <c r="H20">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <v>16</v>
+      </c>
+      <c r="B21">
+        <v>0.64960499999999999</v>
+      </c>
+      <c r="C21">
+        <v>9.77E-4</v>
+      </c>
+      <c r="D21">
+        <v>0.65066199999999996</v>
+      </c>
+      <c r="E21">
+        <v>1.057E-3</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>1.1172489999999999E-6</v>
+      </c>
+      <c r="G21">
+        <v>2933275</v>
+      </c>
+      <c r="H21">
+        <v>1023</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>